--- a/diseases/d045/2000-2004.xlsx
+++ b/diseases/d045/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8381,9 +8339,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8777,9 +8732,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9321,9 +9273,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9717,9 +9666,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10261,9 +10207,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10657,9 +10600,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11201,9 +11141,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11597,9 +11534,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12141,9 +12075,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12537,9 +12468,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13081,9 +13009,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13477,9 +13402,6 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -14021,9 +13943,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14417,9 +14336,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14961,9 +14877,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15357,9 +15270,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15901,9 +15811,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16297,9 +16204,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16841,9 +16745,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17237,9 +17138,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17781,9 +17679,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -18177,9 +18072,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18721,9 +18613,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -19117,9 +19006,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -19661,9 +19547,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -20057,9 +19940,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20601,9 +20481,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -20997,9 +20874,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -21541,9 +21415,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -21937,9 +21808,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -22481,9 +22349,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -22877,9 +22742,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -23421,9 +23283,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -23817,9 +23676,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -24361,9 +24217,6 @@
       <c r="O129" t="n">
         <v>2</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -24757,9 +24610,6 @@
       <c r="O131" t="n">
         <v>4</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -25301,9 +25151,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -25697,9 +25544,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -26241,9 +26085,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26637,9 +26478,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -27181,9 +27019,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -27577,9 +27412,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -28121,9 +27953,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -28517,9 +28346,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -29061,9 +28887,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -29457,9 +29280,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -30001,9 +29821,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -30545,9 +30362,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -31089,9 +30903,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -31633,9 +31444,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -32177,9 +31985,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -32721,9 +32526,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -33265,9 +33067,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -33809,9 +33608,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -34353,9 +34149,6 @@
       <c r="O183" t="n">
         <v>1</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -34897,9 +34690,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -35441,9 +35231,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -35985,9 +35772,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -36529,9 +36313,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -36925,9 +36706,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -37469,9 +37247,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -37865,9 +37640,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -38409,9 +38181,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -38805,9 +38574,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -39349,9 +39115,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -39745,9 +39508,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -40289,9 +40049,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -40685,9 +40442,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -41229,9 +40983,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -41625,9 +41376,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -42169,9 +41917,6 @@
       <c r="O225" t="n">
         <v>1</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -42565,9 +42310,6 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -43109,9 +42851,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -43505,9 +43244,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -44049,9 +43785,6 @@
       <c r="O235" t="n">
         <v>2</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -44445,9 +44178,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -44989,9 +44719,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -45385,9 +45112,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -45929,9 +45653,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -46325,9 +46046,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -46869,9 +46587,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -47263,9 +46978,6 @@
         <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q252" t="n">
         <v>0</v>
       </c>
       <c r="R252" t="n">
